--- a/src/app/modules/dashboard/excel_files/whole-plant-based-hot-and-spicy-recipes.xlsx
+++ b/src/app/modules/dashboard/excel_files/whole-plant-based-hot-and-spicy-recipes.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -9173,7 +9173,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
